--- a/kanban_system/output/library_linked/欧盟法规清单.xlsx
+++ b/kanban_system/output/library_linked/欧盟法规清单.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="欧盟" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="草案" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="欧盟" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="草案" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="更新" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'欧盟'!$A$1:$AB$171</definedName>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">     </t>
+          <t>     </t>
         </is>
       </c>
     </row>
